--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0204.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0204.xlsx
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Bọn ta, dân chài Riccioli, chỉ đánh bắt gần bờ thôi, nên mới dùng thuyền Gondola khi ra khơi.</t>
+          <t>Bọn tao, dân chài Riccioli, chỉ đánh bắt gần bờ thôi, nên mới dùng thuyền Gondola khi ra khơi.</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Sao cơ?</t>
+          <t>Lại đến nữa à?</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Nếu không, lão già điên đó sẽ quay lại bất cứ lúc nào, nhớ lời ta đấy!</t>
+          <t>Nếu không, lão già điên đó sẽ quay lại bất cứ lúc nào, nhớ lời tao đấy!</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Hello?</t>
+          <t>Xin chào?</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Hello?</t>
+          <t>Xin chào?</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Ông già ta thường bảo Queequeg đã làm việc trên con tàu này nhiều năm, sửa chữa nó mà chẳng thay đổi tí gì!</t>
+          <t>Ông già tao thường bảo Queequeg đã làm việc trên con tàu này nhiều năm, sửa chữa nó mà chẳng thay đổi tí gì!</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Đem đống cá chết tiệt ấy đi cho khuất mắt ta! Nhìn nó quẫy đạp thế này là ta nổi da gà rồi đấy!</t>
+          <t>Đem đống cá chết tiệt ấy đi cho khuất mắt tao! Nhìn nó quẫy đạp thế này là tao nổi da gà rồi đấy!</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Cậu nghĩ cái váy này rẻ tiền à? Tiền giặt nó đủ mua hết đống... cá của tụi bay rồi.</t>
+          <t>Mày nghĩ cái váy này rẻ tiền à? Tiền giặt nó đủ mua hết đống... cá của tụi bay rồi.</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Mồm to như cửa hầm của cậu, răng sắc hơn dao. Một phát cắn là nuốt gọn bốn người luôn đấy...</t>
+          <t>Mồm to như cửa hầm của mày, răng sắc hơn dao. Một phát cắn là nuốt gọn bốn người luôn đấy...</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Ta cần ba mươi con Cua Gai, ba mươi con Cua Câm, một thùng Tôm Tiên Tri, và ba con Cá Mặt Trời, tất cả còn sống. Ta sẽ đi cùng ngươi ra thuyền lấy chúng.</t>
+          <t>Tao cần ba mươi con Cua Gai, ba mươi con Cua Câm, một thùng Tôm Tiên Tri, và ba con Cá Mặt Trời, tất cả còn sống. Tao sẽ đi cùng mày ra thuyền lấy chúng.</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Ừ, ném cho ta vài cái đi.</t>
+          <t>Ừ, ném cho tao vài cái đi.</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Bạn đang làm gì ở đây?</t>
+          <t>Cậu làm gì ở đây vậy?</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Này, ta đùa thôi mà! Ta có ăn thật đâu.</t>
+          <t>Này, tao đùa thôi mà! Tao có ăn thật đâu.</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Ta hỏi... cái ngọn hải đăng này, nó đã ở đây từ trước cả khi Ragunna còn chưa thành hình, phải không?</t>
+          <t>Tao hỏi... cái ngọn hải đăng này, nó đã ở đây từ trước cả khi Ragunna còn chưa thành hình, phải không?</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Ôi, giờ cậu nhắc tới thì ta &lt;i&gt;cũng&lt;/i&gt; tò mò muốn đi xem thử.</t>
+          <t>Ôi, giờ cậu nhắc tới thì tao &lt;i&gt;cũng&lt;/i&gt; tò mò muốn đi xem thử.</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Tuy nhiên, ta không khuyến khích đâu. Không biết sao, nhưng chỗ đó luôn khiến ta có cảm giác không ổn...</t>
+          <t>Tuy nhiên, tao không khuyến khích đâu. Không biết sao, nhưng chỗ đó luôn khiến tao có cảm giác không ổn...</t>
         </is>
       </c>
     </row>
@@ -22286,7 +22286,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Đừng kéo ta nữa! Mã khóa buộc sắp đứt rồi!</t>
+          <t>Đừng kéo tao nữa! Mã khóa buộc sắp đứt rồi!</t>
         </is>
       </c>
     </row>
@@ -22546,7 +22546,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Chuyện gì đang xảy ra vậy?</t>
+          <t>Có chuyện gì vậy?</t>
         </is>
       </c>
     </row>
@@ -22806,7 +22806,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Ê! Ta là người phụ trách ở đây!</t>
+          <t>Ê! Tao là người phụ trách ở đây!</t>
         </is>
       </c>
     </row>
@@ -23131,7 +23131,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Lỗi của cậu chứ không phải của ta!</t>
+          <t>Lỗi của cậu chứ không phải của tao!</t>
         </is>
       </c>
     </row>
@@ -23261,7 +23261,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Nhưng ta vẫn luôn dùng nó mà!</t>
+          <t>Nhưng tao vẫn luôn dùng nó mà!</t>
         </is>
       </c>
     </row>
@@ -23326,7 +23326,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Không có nghĩa là nó thuộc về cậu!</t>
+          <t>Không có nghĩa là nó thuộc về mày!</t>
         </is>
       </c>
     </row>
@@ -23391,7 +23391,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Bọn cậu cãi nhau chuyện gì vậy?</t>
+          <t>Bọn mày cãi nhau chuyện gì vậy?</t>
         </is>
       </c>
     </row>
@@ -24431,7 +24431,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Hai người đó á? Thật sao? Để ta kiểm tra họ một chút.</t>
+          <t>Hai người đó á? Thật sao? Để tao kiểm tra họ một chút.</t>
         </is>
       </c>
     </row>
@@ -25471,7 +25471,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Ta hiểu lo lắng của cậu, nhưng thay vì kìm hãm, chúng ta nên tìm cách thích nghi và tiến lên.</t>
+          <t>Tao hiểu lo lắng của cậu, nhưng thay vì kìm hãm, chúng ta nên tìm cách thích nghi và tiến lên.</t>
         </is>
       </c>
     </row>
@@ -26186,7 +26186,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Một... Cậu có thể ngừng hỏi ta những câu kỳ cục thế này không? Đầu ta đau quá...</t>
+          <t>Một... Cậu có thể ngừng hỏi tao những câu kỳ cục thế này không? Đầu tao đau quá...</t>
         </is>
       </c>
     </row>
@@ -26641,7 +26641,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Đúng vậy. Những Cộng Hưởng Giả được phân công thu thập Reverberation thường có giác quan nhạy bén, có thể phát hiện cả lượng tần số còn sót lại dù là nhỏ nhất.</t>
+          <t>Đúng vậy. Những Resonator được phân công thu thập Reverberation thường có giác quan nhạy bén, có thể phát hiện cả lượng tần số còn sót lại dù là nhỏ nhất.</t>
         </is>
       </c>
     </row>
@@ -26771,7 +26771,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>...Ta cũng từng cảm nhận sức nặng của những cảm xúc đọng lại như thế. Nên nếu cậu cần ai đó để tâm sự, ta ở đây.</t>
+          <t>...Tao cũng từng cảm nhận sức nặng của những cảm xúc đọng lại như thế. Nên nếu cậu cần ai đó để tâm sự, tao ở đây.</t>
         </is>
       </c>
     </row>
@@ -27291,7 +27291,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Tất nhiên là ta có thật mà.</t>
+          <t>Tất nhiên là tao có thật mà.</t>
         </is>
       </c>
     </row>
@@ -27486,7 +27486,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Đừng lo, {Male=anh ấy;Female=cô ấy} là người thật mà.</t>
+          <t>Đừng lo, {Male=he's;Female=she's} là người thật mà.</t>
         </is>
       </c>
     </row>
@@ -27941,7 +27941,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Thật đấy, tin ta đi.</t>
+          <t>Thật đấy, tin tao đi.</t>
         </is>
       </c>
     </row>
@@ -29241,7 +29241,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Dù sao thì ta cũng phải kiểm tra kho hàng. Nếu ngươi có kiện gì cần gửi thì cứ tìm ta nhé.</t>
+          <t>Dù sao thì tao cũng phải kiểm tra kho hàng. Nếu mày có kiện gì cần gửi thì cứ tìm tao nhé.</t>
         </is>
       </c>
     </row>
@@ -30996,7 +30996,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>...Đùa hoài về tên ta như vậy chẳng vui đâu.</t>
+          <t>...Đùa hoài về tên tao như vậy chẳng vui đâu.</t>
         </is>
       </c>
     </row>
@@ -32556,7 +32556,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Lần tới nghỉ phép, chúng ta nhất định phải đến Kim Châu và thử các món đặc sản ở đó nhé!</t>
+          <t>Lần tới nghỉ phép, chúng ta nhất định phải đến Jinzhou và thử các món đặc sản ở đó nhé!</t>
         </is>
       </c>
     </row>
@@ -32686,7 +32686,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Bạn đang làm gì ở đây?</t>
+          <t>Cậu làm gì ở đây vậy?</t>
         </is>
       </c>
     </row>
